--- a/output/stock_quant_scores/VRTX_info.xlsx
+++ b/output/stock_quant_scores/VRTX_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FM2"/>
+  <dimension ref="A1:FQ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1046,225 +1046,245 @@
       </c>
       <c r="DU1" s="1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1390,28 +1410,28 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
+        <v>381.87</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>381.91</v>
+      </c>
+      <c r="AE2" t="n">
         <v>379.72</v>
       </c>
-      <c r="AD2" t="n">
-        <v>377.56</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>374.17</v>
-      </c>
       <c r="AF2" t="n">
-        <v>380.725</v>
+        <v>387.48</v>
       </c>
       <c r="AG2" t="n">
+        <v>381.87</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>381.91</v>
+      </c>
+      <c r="AI2" t="n">
         <v>379.72</v>
       </c>
-      <c r="AH2" t="n">
-        <v>377.56</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>374.17</v>
-      </c>
       <c r="AJ2" t="n">
-        <v>380.725</v>
+        <v>387.48</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -1420,31 +1440,31 @@
         <v>0.439</v>
       </c>
       <c r="AM2" t="n">
-        <v>26.72847</v>
+        <v>27.474</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.007193</v>
+        <v>20.550611</v>
       </c>
       <c r="AO2" t="n">
-        <v>792696</v>
+        <v>1838533</v>
       </c>
       <c r="AP2" t="n">
-        <v>792696</v>
+        <v>1838533</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1726130</v>
+        <v>1728404</v>
       </c>
       <c r="AR2" t="n">
-        <v>1739220</v>
+        <v>1957630</v>
       </c>
       <c r="AS2" t="n">
-        <v>1739220</v>
+        <v>1957630</v>
       </c>
       <c r="AT2" t="n">
-        <v>357.37</v>
+        <v>367.81</v>
       </c>
       <c r="AU2" t="n">
-        <v>400.25</v>
+        <v>402.68</v>
       </c>
       <c r="AV2" t="n">
         <v>1</v>
@@ -1453,7 +1473,7 @@
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>96283664384</v>
+        <v>98898845696</v>
       </c>
       <c r="AY2" t="n">
         <v>362.5</v>
@@ -1468,13 +1488,13 @@
         <v>3.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.432029999999999</v>
+        <v>8.661054</v>
       </c>
       <c r="BD2" t="n">
-        <v>412.4306</v>
+        <v>407.3748</v>
       </c>
       <c r="BE2" t="n">
-        <v>448.43085</v>
+        <v>447.222</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
@@ -1491,7 +1511,7 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>92501254144</v>
+        <v>94043447296</v>
       </c>
       <c r="BK2" t="n">
         <v>0.31856</v>
@@ -1503,31 +1523,31 @@
         <v>256390651</v>
       </c>
       <c r="BN2" t="n">
-        <v>3639292</v>
+        <v>4053668</v>
       </c>
       <c r="BO2" t="n">
-        <v>4362540</v>
+        <v>3700693</v>
       </c>
       <c r="BP2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.014199999</v>
+        <v>0.015800001</v>
       </c>
       <c r="BS2" t="n">
         <v>0.0014399999</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.98167</v>
+        <v>0.98143</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.54</v>
+        <v>2.83</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.016</v>
+        <v>0.0178</v>
       </c>
       <c r="BW2" t="n">
         <v>256390651</v>
@@ -1536,7 +1556,7 @@
         <v>67.015</v>
       </c>
       <c r="BY2" t="n">
-        <v>5.6037455</v>
+        <v>5.75595</v>
       </c>
       <c r="BZ2" t="n">
         <v>1735603200</v>
@@ -1551,7 +1571,7 @@
         <v>3637600000</v>
       </c>
       <c r="CD2" t="n">
-        <v>14.05</v>
+        <v>14.04</v>
       </c>
       <c r="CE2" t="n">
         <v>18.77</v>
@@ -1565,16 +1585,16 @@
         <v>967075200</v>
       </c>
       <c r="CH2" t="n">
-        <v>8.101000000000001</v>
+        <v>8.236000000000001</v>
       </c>
       <c r="CI2" t="n">
-        <v>19.265</v>
+        <v>19.587</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0.17766804</v>
+        <v>-0.17059433</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
@@ -1582,7 +1602,7 @@
         </is>
       </c>
       <c r="CM2" t="n">
-        <v>375.535</v>
+        <v>385.735</v>
       </c>
       <c r="CN2" t="n">
         <v>624</v>
@@ -1591,13 +1611,13 @@
         <v>330</v>
       </c>
       <c r="CP2" t="n">
-        <v>479.64</v>
+        <v>479.56</v>
       </c>
       <c r="CQ2" t="n">
         <v>478</v>
       </c>
       <c r="CR2" t="n">
-        <v>2</v>
+        <v>1.9375</v>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -1641,7 +1661,7 @@
         <v>0.22771</v>
       </c>
       <c r="DF2" t="n">
-        <v>6383799808</v>
+        <v>5999600128</v>
       </c>
       <c r="DG2" t="n">
         <v>2914625024</v>
@@ -1653,7 +1673,7 @@
         <v>0.121</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.55906</v>
+        <v>0.52541</v>
       </c>
       <c r="DK2" t="n">
         <v>0.42048</v>
@@ -1701,163 +1721,175 @@
       </c>
       <c r="DU2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DV2" t="n">
-        <v>1758740024</v>
-      </c>
-      <c r="DW2" t="inlineStr">
+      <c r="DW2" t="n">
+        <v>1758930965</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1758916800</v>
+      </c>
+      <c r="DY2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>680362200000</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-1.4867682</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>380</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-5.7349854</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>3.86499</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>379.72 - 387.48</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>NasdaqGS</t>
+        </is>
+      </c>
+      <c r="EG2" t="n">
+        <v>1728404</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>23.234985</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>0.06409651</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>362.5 - 519.88</t>
+        </is>
+      </c>
+      <c r="EK2" t="n">
+        <v>-134.14502</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-0.25803074</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-17.059433</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1754337600</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1754337600</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1754337600</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1754339400</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>1754339400</v>
+      </c>
+      <c r="ES2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>Vertex Pharmaceuticals Incorpor</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>Vertex Pharmaceuticals Incorporated</t>
+        </is>
+      </c>
+      <c r="EW2" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>18.03271</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>21.39085</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>-21.639801</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>-0.05312013</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>-61.487</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>-0.13748653</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG2" t="inlineStr">
+        <is>
+          <t>1.9 - Buy</t>
+        </is>
+      </c>
+      <c r="FH2" t="inlineStr">
         <is>
           <t>NMS</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="FI2" t="inlineStr">
         <is>
           <t>finmb_36235</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
+      <c r="FJ2" t="inlineStr">
         <is>
           <t>America/New_York</t>
         </is>
       </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="FK2" t="inlineStr">
         <is>
           <t>EDT</t>
         </is>
       </c>
-      <c r="EA2" t="n">
+      <c r="FL2" t="n">
         <v>-14400000</v>
       </c>
-      <c r="EB2" t="inlineStr">
+      <c r="FM2" t="inlineStr">
         <is>
           <t>us_market</t>
         </is>
       </c>
-      <c r="EC2" t="b">
+      <c r="FN2" t="b">
         <v>0</v>
       </c>
-      <c r="ED2" t="n">
-        <v>14.05</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>18.77</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>18.03271</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>20.825212</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-36.8956</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.08945893000000001</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-72.89584000000001</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-0.1625576</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>2.0 - Buy</t>
-        </is>
-      </c>
-      <c r="EO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EP2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>680362200000</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>-4.1849976</v>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>374.17 - 380.725</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>NasdaqGS</t>
-        </is>
-      </c>
-      <c r="EU2" t="n">
-        <v>1726130</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>13.035004</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>0.03595863</v>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>362.5 - 519.88</t>
-        </is>
-      </c>
-      <c r="EY2" t="n">
-        <v>-144.345</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>-0.27765062</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>-17.766804</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>1754337600</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>1754337600</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>1754337600</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>1754339400</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>1754339400</v>
-      </c>
-      <c r="FG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FH2" t="inlineStr">
-        <is>
-          <t>Vertex Pharmaceuticals Incorpor</t>
-        </is>
-      </c>
-      <c r="FI2" t="inlineStr">
-        <is>
-          <t>Vertex Pharmaceuticals Incorporated</t>
-        </is>
-      </c>
-      <c r="FJ2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="FK2" t="n">
-        <v>-1.1021272</v>
-      </c>
-      <c r="FL2" t="n">
-        <v>375.535</v>
-      </c>
-      <c r="FM2" t="inlineStr"/>
+      <c r="FO2" t="n">
+        <v>1.01212</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>385.735</v>
+      </c>
+      <c r="FQ2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
